--- a/data/human_baseline_annotations/annotation_annotator1.xlsx
+++ b/data/human_baseline_annotations/annotation_annotator1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/railey/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8DC98A-435C-AA47-BCF7-4B30180B25B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF18048-F555-1041-B66D-FDCAA0F964A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1800" windowWidth="10440" windowHeight="16660" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1800" windowWidth="10440" windowHeight="16660" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -15626,7 +15626,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -15654,6 +15654,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -45185,7 +45191,7 @@
   <sheetPr>
     <tabColor rgb="FFBDD7EE"/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -45240,7 +45246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1539</v>
       </c>
@@ -45279,7 +45285,7 @@
       </c>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1547</v>
       </c>
@@ -45318,7 +45324,7 @@
       </c>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>1553</v>
       </c>
@@ -45357,7 +45363,7 @@
       </c>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>1559</v>
       </c>
@@ -45392,11 +45398,11 @@
         <v>32</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>1565</v>
       </c>
@@ -45435,7 +45441,7 @@
       </c>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>1572</v>
       </c>
@@ -45474,7 +45480,7 @@
       </c>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>1578</v>
       </c>
@@ -45513,7 +45519,7 @@
       </c>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>1584</v>
       </c>
@@ -45550,9 +45556,9 @@
       <c r="L9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="M9" s="12"/>
+    </row>
+    <row r="10" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>1590</v>
       </c>
@@ -45589,9 +45595,9 @@
       <c r="L10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="M10" s="12"/>
+    </row>
+    <row r="11" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>1597</v>
       </c>
@@ -45628,9 +45634,9 @@
       <c r="L11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="M11" s="12"/>
+    </row>
+    <row r="12" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>1600</v>
       </c>
@@ -45661,11 +45667,11 @@
         <v>32</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="M12" s="12"/>
+    </row>
+    <row r="13" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>1606</v>
       </c>
@@ -45696,11 +45702,11 @@
         <v>40</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+      <c r="M13" s="12"/>
+    </row>
+    <row r="14" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>1611</v>
       </c>
@@ -45731,11 +45737,11 @@
         <v>40</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+      <c r="M14" s="12"/>
+    </row>
+    <row r="15" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>1615</v>
       </c>
@@ -45768,9 +45774,9 @@
       <c r="L15" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>1618</v>
       </c>
@@ -45801,11 +45807,11 @@
         <v>32</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="M16" s="12"/>
+    </row>
+    <row r="17" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>1621</v>
       </c>
@@ -45836,11 +45842,11 @@
         <v>40</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+      <c r="M17" s="12"/>
+    </row>
+    <row r="18" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>1626</v>
       </c>
@@ -45871,11 +45877,11 @@
         <v>32</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="M18" s="12"/>
+    </row>
+    <row r="19" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>1629</v>
       </c>
@@ -45906,11 +45912,11 @@
         <v>32</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+      <c r="M19" s="12"/>
+    </row>
+    <row r="20" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>1634</v>
       </c>
@@ -45941,11 +45947,11 @@
         <v>32</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="M20" s="12"/>
+    </row>
+    <row r="21" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>1638</v>
       </c>
@@ -45976,9 +45982,15 @@
         <v>40</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M21" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="M21" s="12"/>
+    </row>
+    <row r="22" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M22" s="13"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="13"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/data/human_baseline_annotations/annotation_annotator1.xlsx
+++ b/data/human_baseline_annotations/annotation_annotator1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/railey/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/railey/Documents/pacute/pacute-bench/data/human_baseline_annotations/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF18048-F555-1041-B66D-FDCAA0F964A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1800" windowWidth="10440" windowHeight="16660" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1800" windowWidth="34020" windowHeight="20060" firstSheet="6" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
